--- a/Results/Phase 2/Methanol/methanol ionising radiation results.xlsx
+++ b/Results/Phase 2/Methanol/methanol ionising radiation results.xlsx
@@ -3314,85 +3314,85 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.04127634272756735</v>
+        <v>0.04110086556142997</v>
       </c>
       <c r="C33" t="n">
-        <v>0.03809847333202691</v>
+        <v>0.03757886807771465</v>
       </c>
       <c r="D33" t="n">
-        <v>0.04260580120881923</v>
+        <v>0.0418637965711452</v>
       </c>
       <c r="E33" t="n">
-        <v>0.03239773159096646</v>
+        <v>0.02486943489467367</v>
       </c>
       <c r="F33" t="n">
-        <v>0.0439072004281234</v>
+        <v>0.04260441333596139</v>
       </c>
       <c r="G33" t="n">
-        <v>0.04387140365195631</v>
+        <v>0.04267026380754151</v>
       </c>
       <c r="H33" t="n">
-        <v>0.04784782062636544</v>
+        <v>0.04484712531257565</v>
       </c>
       <c r="I33" t="n">
-        <v>0.0431360386658286</v>
+        <v>0.04216615078606335</v>
       </c>
       <c r="J33" t="n">
-        <v>0.04798941663991384</v>
+        <v>0.0451308523807228</v>
       </c>
       <c r="K33" t="n">
-        <v>0.04624944403129228</v>
+        <v>0.04399496295222407</v>
       </c>
       <c r="L33" t="n">
-        <v>0.04159273712717339</v>
+        <v>0.04128415003967552</v>
       </c>
       <c r="M33" t="n">
-        <v>0.04667486270848741</v>
+        <v>0.04421539450420326</v>
       </c>
       <c r="N33" t="n">
-        <v>0.04478165720043845</v>
+        <v>0.04315767043196692</v>
       </c>
       <c r="O33" t="n">
-        <v>0.05074842664149121</v>
+        <v>0.04819306961635189</v>
       </c>
       <c r="P33" t="n">
-        <v>0.05457898909813033</v>
+        <v>0.04918696326658178</v>
       </c>
       <c r="Q33" t="n">
-        <v>0.04459092667204798</v>
+        <v>0.04303813033999272</v>
       </c>
       <c r="R33" t="n">
-        <v>0.0450842783869104</v>
+        <v>0.0432817785773833</v>
       </c>
       <c r="S33" t="n">
-        <v>0.04135141984705219</v>
+        <v>0.04114405305674623</v>
       </c>
       <c r="T33" t="n">
-        <v>0.05052328303598317</v>
+        <v>0.04646309623959164</v>
       </c>
       <c r="U33" t="n">
-        <v>0.221747223038283</v>
+        <v>0.2185515294052456</v>
       </c>
       <c r="V33" t="n">
-        <v>0.05158761615106437</v>
+        <v>0.04739145331343251</v>
       </c>
       <c r="W33" t="n">
-        <v>0.2537951450913927</v>
+        <v>0.2455511168669131</v>
       </c>
       <c r="X33" t="n">
-        <v>0.04133470454013223</v>
+        <v>0.04112510376406243</v>
       </c>
       <c r="Y33" t="n">
-        <v>0.05961646786300504</v>
+        <v>0.05197722014361723</v>
       </c>
       <c r="Z33" t="n">
-        <v>0.2088626618889574</v>
+        <v>0.2041155577457089</v>
       </c>
       <c r="AA33" t="n">
-        <v>0.04269838701607764</v>
+        <v>0.04193572937955613</v>
       </c>
       <c r="AB33" t="n">
-        <v>0.04253563729931936</v>
+        <v>0.04180504812053931</v>
       </c>
     </row>
   </sheetData>
@@ -6286,85 +6286,85 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.04044760113269053</v>
+        <v>0.04039131746524752</v>
       </c>
       <c r="C33" t="n">
-        <v>0.03708846600441366</v>
+        <v>0.03671655505224884</v>
       </c>
       <c r="D33" t="n">
-        <v>0.04113176908528195</v>
+        <v>0.04079580247526062</v>
       </c>
       <c r="E33" t="n">
-        <v>0.01663800113220454</v>
+        <v>0.01526143349384416</v>
       </c>
       <c r="F33" t="n">
-        <v>0.06027464948915553</v>
+        <v>0.0520906083615901</v>
       </c>
       <c r="G33" t="n">
-        <v>0.04842719332925055</v>
+        <v>0.04537038135684352</v>
       </c>
       <c r="H33" t="n">
-        <v>0.04544877772677011</v>
+        <v>0.04327815867590614</v>
       </c>
       <c r="I33" t="n">
-        <v>0.04347893729304678</v>
+        <v>0.04216822882876114</v>
       </c>
       <c r="J33" t="n">
-        <v>0.04861935084619192</v>
+        <v>0.04535628879202274</v>
       </c>
       <c r="K33" t="n">
-        <v>0.05156806664833791</v>
+        <v>0.04723875167195892</v>
       </c>
       <c r="L33" t="n">
-        <v>0.0484493043391121</v>
+        <v>0.04533092583879562</v>
       </c>
       <c r="M33" t="n">
-        <v>0.05440964259148445</v>
+        <v>0.04867360792217687</v>
       </c>
       <c r="N33" t="n">
-        <v>0.04711370072120133</v>
+        <v>0.04431157575025671</v>
       </c>
       <c r="O33" t="n">
-        <v>0.07788184073232787</v>
+        <v>0.06689671114841136</v>
       </c>
       <c r="P33" t="n">
-        <v>0.05927648238647438</v>
+        <v>0.0520854999735233</v>
       </c>
       <c r="Q33" t="n">
-        <v>0.04524787850776137</v>
+        <v>0.04329067429496598</v>
       </c>
       <c r="R33" t="n">
-        <v>0.04363424722163343</v>
+        <v>0.04223640064188455</v>
       </c>
       <c r="S33" t="n">
-        <v>0.05040821991829889</v>
+        <v>0.04656677003440254</v>
       </c>
       <c r="T33" t="n">
-        <v>0.05481559563439346</v>
+        <v>0.04878765406758694</v>
       </c>
       <c r="U33" t="n">
-        <v>0.2212002776868896</v>
+        <v>0.2175218314271198</v>
       </c>
       <c r="V33" t="n">
-        <v>0.04311575180136021</v>
+        <v>0.04204719091713281</v>
       </c>
       <c r="W33" t="n">
-        <v>0.2419194311293148</v>
+        <v>0.2374597030659983</v>
       </c>
       <c r="X33" t="n">
-        <v>0.04995744248468046</v>
+        <v>0.04609957536612644</v>
       </c>
       <c r="Y33" t="n">
-        <v>0.04833811530254603</v>
+        <v>0.04505144996949612</v>
       </c>
       <c r="Z33" t="n">
-        <v>0.1951567716447849</v>
+        <v>0.1944385444036897</v>
       </c>
       <c r="AA33" t="n">
-        <v>0.04284398061425048</v>
+        <v>0.04180933945933056</v>
       </c>
       <c r="AB33" t="n">
-        <v>0.04665564324059838</v>
+        <v>0.04397541102109787</v>
       </c>
     </row>
   </sheetData>
@@ -9258,85 +9258,85 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.04104150031802686</v>
+        <v>0.04093032636621868</v>
       </c>
       <c r="C33" t="n">
-        <v>0.0385296737481076</v>
+        <v>0.03781540906777221</v>
       </c>
       <c r="D33" t="n">
-        <v>0.04137148352192225</v>
+        <v>0.0411162589210417</v>
       </c>
       <c r="E33" t="n">
-        <v>0.03049247640266687</v>
+        <v>0.02369277054738076</v>
       </c>
       <c r="F33" t="n">
-        <v>0.04375663907305199</v>
+        <v>0.04250273891425435</v>
       </c>
       <c r="G33" t="n">
-        <v>0.04317322378886655</v>
+        <v>0.04222493526129834</v>
       </c>
       <c r="H33" t="n">
-        <v>0.04777635395322614</v>
+        <v>0.04478335453779118</v>
       </c>
       <c r="I33" t="n">
-        <v>0.04370170283731926</v>
+        <v>0.04246454663246732</v>
       </c>
       <c r="J33" t="n">
-        <v>0.04706422082291522</v>
+        <v>0.04456506358711364</v>
       </c>
       <c r="K33" t="n">
-        <v>0.04491243901324792</v>
+        <v>0.04324828485041989</v>
       </c>
       <c r="L33" t="n">
-        <v>0.04118705871838069</v>
+        <v>0.04101447026573742</v>
       </c>
       <c r="M33" t="n">
-        <v>0.04461678193946086</v>
+        <v>0.04299828779855337</v>
       </c>
       <c r="N33" t="n">
-        <v>0.04371447899631314</v>
+        <v>0.0425006075908609</v>
       </c>
       <c r="O33" t="n">
-        <v>0.06399764821869539</v>
+        <v>0.05740447378831372</v>
       </c>
       <c r="P33" t="n">
-        <v>0.05329533979845384</v>
+        <v>0.04838725319594976</v>
       </c>
       <c r="Q33" t="n">
-        <v>0.04767237076197157</v>
+        <v>0.04482751403797476</v>
       </c>
       <c r="R33" t="n">
-        <v>0.04625324778302171</v>
+        <v>0.04392588116832789</v>
       </c>
       <c r="S33" t="n">
-        <v>0.04119310761482924</v>
+        <v>0.04102133377121758</v>
       </c>
       <c r="T33" t="n">
-        <v>0.04939673360624976</v>
+        <v>0.04579041741149222</v>
       </c>
       <c r="U33" t="n">
-        <v>0.2209549138476558</v>
+        <v>0.2180120086010786</v>
       </c>
       <c r="V33" t="n">
-        <v>0.05253868909799692</v>
+        <v>0.04804777991332192</v>
       </c>
       <c r="W33" t="n">
-        <v>0.2520068355852488</v>
+        <v>0.2443982153926843</v>
       </c>
       <c r="X33" t="n">
-        <v>0.04130879532001174</v>
+        <v>0.04108145523791115</v>
       </c>
       <c r="Y33" t="n">
-        <v>0.05972844237761517</v>
+        <v>0.05206418273949973</v>
       </c>
       <c r="Z33" t="n">
-        <v>0.2083313112946839</v>
+        <v>0.203776802655674</v>
       </c>
       <c r="AA33" t="n">
-        <v>0.04331239042357772</v>
+        <v>0.0422751274663332</v>
       </c>
       <c r="AB33" t="n">
-        <v>0.04237908131797365</v>
+        <v>0.04168548735117926</v>
       </c>
     </row>
   </sheetData>
@@ -12230,85 +12230,85 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.04090427773458748</v>
+        <v>0.04067133429122224</v>
       </c>
       <c r="C33" t="n">
-        <v>0.03764663362483786</v>
+        <v>0.03709438093070219</v>
       </c>
       <c r="D33" t="n">
-        <v>0.04106208675865194</v>
+        <v>0.04074929385282824</v>
       </c>
       <c r="E33" t="n">
-        <v>0.02251312595201272</v>
+        <v>0.01871061080255099</v>
       </c>
       <c r="F33" t="n">
-        <v>0.05131877058658868</v>
+        <v>0.04675386331549568</v>
       </c>
       <c r="G33" t="n">
-        <v>0.04223604957696298</v>
+        <v>0.04148567843988712</v>
       </c>
       <c r="H33" t="n">
-        <v>0.04697376192200142</v>
+        <v>0.04412094072449487</v>
       </c>
       <c r="I33" t="n">
-        <v>0.04225937351255619</v>
+        <v>0.04144141903863289</v>
       </c>
       <c r="J33" t="n">
-        <v>0.04522761272375551</v>
+        <v>0.04328157211754224</v>
       </c>
       <c r="K33" t="n">
-        <v>0.04096268256888192</v>
+        <v>0.04070229240873339</v>
       </c>
       <c r="L33" t="n">
-        <v>0.04053884081283002</v>
+        <v>0.0404464996322924</v>
       </c>
       <c r="M33" t="n">
-        <v>0.04355826397872065</v>
+        <v>0.04219409012451363</v>
       </c>
       <c r="N33" t="n">
-        <v>0.04281856317259757</v>
+        <v>0.04178695824472375</v>
       </c>
       <c r="O33" t="n">
-        <v>0.07076058088889531</v>
+        <v>0.06189016490481927</v>
       </c>
       <c r="P33" t="n">
-        <v>0.05161120630113755</v>
+        <v>0.04721890290694613</v>
       </c>
       <c r="Q33" t="n">
-        <v>0.05326628847170081</v>
+        <v>0.04799869404889284</v>
       </c>
       <c r="R33" t="n">
-        <v>0.04524712683903855</v>
+        <v>0.04315547766272284</v>
       </c>
       <c r="S33" t="n">
-        <v>0.04065801198817456</v>
+        <v>0.0405204470748137</v>
       </c>
       <c r="T33" t="n">
-        <v>0.05187792990212906</v>
+        <v>0.0470415224103007</v>
       </c>
       <c r="U33" t="n">
-        <v>0.2184534866850143</v>
+        <v>0.2160789914927061</v>
       </c>
       <c r="V33" t="n">
-        <v>0.04909797046430983</v>
+        <v>0.04577522290937255</v>
       </c>
       <c r="W33" t="n">
-        <v>0.2474051915437065</v>
+        <v>0.241165691612398</v>
       </c>
       <c r="X33" t="n">
-        <v>0.04115362205262207</v>
+        <v>0.04080532608396133</v>
       </c>
       <c r="Y33" t="n">
-        <v>0.05409205071072411</v>
+        <v>0.0485138792998888</v>
       </c>
       <c r="Z33" t="n">
-        <v>0.2018684165665983</v>
+        <v>0.1992870654609456</v>
       </c>
       <c r="AA33" t="n">
-        <v>0.04277577602945706</v>
+        <v>0.04177244561163242</v>
       </c>
       <c r="AB33" t="n">
-        <v>0.04159989359133805</v>
+        <v>0.04104651988893117</v>
       </c>
     </row>
   </sheetData>
@@ -15202,85 +15202,85 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.0406498981817092</v>
+        <v>0.04030397311867733</v>
       </c>
       <c r="C33" t="n">
-        <v>0.03669964344689525</v>
+        <v>0.03629646034717087</v>
       </c>
       <c r="D33" t="n">
-        <v>0.04237123857704391</v>
+        <v>0.04130638498788165</v>
       </c>
       <c r="E33" t="n">
-        <v>0.01555001397751071</v>
+        <v>0.01439291529432218</v>
       </c>
       <c r="F33" t="n">
-        <v>0.05559903792184116</v>
+        <v>0.04905967103858572</v>
       </c>
       <c r="G33" t="n">
-        <v>0.04191166496232305</v>
+        <v>0.04108643412337373</v>
       </c>
       <c r="H33" t="n">
-        <v>0.0462247103898723</v>
+        <v>0.04344846062948438</v>
       </c>
       <c r="I33" t="n">
-        <v>0.04793843597113916</v>
+        <v>0.04453735490908781</v>
       </c>
       <c r="J33" t="n">
-        <v>0.04450790783958767</v>
+        <v>0.04260705162446805</v>
       </c>
       <c r="K33" t="n">
-        <v>0.04583889476229473</v>
+        <v>0.04346658956458972</v>
       </c>
       <c r="L33" t="n">
-        <v>0.04521789617103551</v>
+        <v>0.04306134922222955</v>
       </c>
       <c r="M33" t="n">
-        <v>0.04675372720766013</v>
+        <v>0.04388203788411044</v>
       </c>
       <c r="N33" t="n">
-        <v>0.04176809735099458</v>
+        <v>0.04093746493915446</v>
       </c>
       <c r="O33" t="n">
-        <v>0.06148005566656552</v>
+        <v>0.05505403151693642</v>
       </c>
       <c r="P33" t="n">
-        <v>0.04808183788594621</v>
+        <v>0.04491100781954631</v>
       </c>
       <c r="Q33" t="n">
-        <v>0.05502854693989058</v>
+        <v>0.04890851474970698</v>
       </c>
       <c r="R33" t="n">
-        <v>0.04657104611261985</v>
+        <v>0.04368164298708363</v>
       </c>
       <c r="S33" t="n">
-        <v>0.04484683951628681</v>
+        <v>0.04286936847528209</v>
       </c>
       <c r="T33" t="n">
-        <v>0.05272309995258827</v>
+        <v>0.04729591905836165</v>
       </c>
       <c r="U33" t="n">
-        <v>0.2138570408720743</v>
+        <v>0.2127384877252083</v>
       </c>
       <c r="V33" t="n">
-        <v>0.0424232669020945</v>
+        <v>0.0414161078750092</v>
       </c>
       <c r="W33" t="n">
-        <v>0.2420731142334298</v>
+        <v>0.2373602828162061</v>
       </c>
       <c r="X33" t="n">
-        <v>0.04211916240840374</v>
+        <v>0.04115866156434159</v>
       </c>
       <c r="Y33" t="n">
-        <v>0.04336595807017579</v>
+        <v>0.04188654583772599</v>
       </c>
       <c r="Z33" t="n">
-        <v>0.1950761446804238</v>
+        <v>0.1943115391982494</v>
       </c>
       <c r="AA33" t="n">
-        <v>0.04244833417804898</v>
+        <v>0.04134759329007565</v>
       </c>
       <c r="AB33" t="n">
-        <v>0.04081677172089643</v>
+        <v>0.04036292883568375</v>
       </c>
     </row>
   </sheetData>
@@ -18174,85 +18174,85 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.04184468276236373</v>
+        <v>0.04170483858764628</v>
       </c>
       <c r="C33" t="n">
-        <v>0.03862494477435238</v>
+        <v>0.03809002509541627</v>
       </c>
       <c r="D33" t="n">
-        <v>0.04275778201576037</v>
+        <v>0.04223223256674668</v>
       </c>
       <c r="E33" t="n">
-        <v>0.03310889569039344</v>
+        <v>0.02550716154364403</v>
       </c>
       <c r="F33" t="n">
-        <v>0.04584986568179723</v>
+        <v>0.04404724842514729</v>
       </c>
       <c r="G33" t="n">
-        <v>0.04834167488434199</v>
+        <v>0.04579903997055652</v>
       </c>
       <c r="H33" t="n">
-        <v>0.04464404565851905</v>
+        <v>0.04330155552846041</v>
       </c>
       <c r="I33" t="n">
-        <v>0.04350192433083214</v>
+        <v>0.04266153204933754</v>
       </c>
       <c r="J33" t="n">
-        <v>0.05247363045333174</v>
+        <v>0.04822545362818406</v>
       </c>
       <c r="K33" t="n">
-        <v>0.04382246421492679</v>
+        <v>0.04289887861944622</v>
       </c>
       <c r="L33" t="n">
-        <v>0.04215570675186229</v>
+        <v>0.04189276384683391</v>
       </c>
       <c r="M33" t="n">
-        <v>0.05646487078676089</v>
+        <v>0.05053882942710042</v>
       </c>
       <c r="N33" t="n">
-        <v>0.05207115984685148</v>
+        <v>0.04780176017178739</v>
       </c>
       <c r="O33" t="n">
-        <v>0.08919306534987745</v>
+        <v>0.07547914535772655</v>
       </c>
       <c r="P33" t="n">
-        <v>0.06615612231415081</v>
+        <v>0.05655995500546628</v>
       </c>
       <c r="Q33" t="n">
-        <v>0.0560426914178556</v>
+        <v>0.05021930377673909</v>
       </c>
       <c r="R33" t="n">
-        <v>0.04389790948160859</v>
+        <v>0.04287895086184427</v>
       </c>
       <c r="S33" t="n">
-        <v>0.04233432594324548</v>
+        <v>0.0420168279209329</v>
       </c>
       <c r="T33" t="n">
-        <v>0.05760339779340632</v>
+        <v>0.0510767112714191</v>
       </c>
       <c r="U33" t="n">
-        <v>0.2260219749865104</v>
+        <v>0.2215546779423453</v>
       </c>
       <c r="V33" t="n">
-        <v>0.05406018631266097</v>
+        <v>0.04928095888094199</v>
       </c>
       <c r="W33" t="n">
-        <v>0.2617132075561173</v>
+        <v>0.2506696866521648</v>
       </c>
       <c r="X33" t="n">
-        <v>0.04221956277872226</v>
+        <v>0.04191905563502624</v>
       </c>
       <c r="Y33" t="n">
-        <v>0.06486428774749219</v>
+        <v>0.05543406295867986</v>
       </c>
       <c r="Z33" t="n">
-        <v>0.211189026471045</v>
+        <v>0.2060591785394635</v>
       </c>
       <c r="AA33" t="n">
-        <v>0.04408446758738406</v>
+        <v>0.0430313838120589</v>
       </c>
       <c r="AB33" t="n">
-        <v>0.05274463044436519</v>
+        <v>0.04803006577368093</v>
       </c>
     </row>
   </sheetData>
@@ -21146,85 +21146,85 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.04084166664910389</v>
+        <v>0.04075394885291853</v>
       </c>
       <c r="C33" t="n">
-        <v>0.03777285615654375</v>
+        <v>0.0372466989336769</v>
       </c>
       <c r="D33" t="n">
-        <v>0.04112811679269091</v>
+        <v>0.04091940971662457</v>
       </c>
       <c r="E33" t="n">
-        <v>0.01958309441053081</v>
+        <v>0.01705633732249211</v>
       </c>
       <c r="F33" t="n">
-        <v>0.05111474639103517</v>
+        <v>0.04684371137469363</v>
       </c>
       <c r="G33" t="n">
-        <v>0.04718693700994843</v>
+        <v>0.0447979971526086</v>
       </c>
       <c r="H33" t="n">
-        <v>0.04271664606260157</v>
+        <v>0.04182993009065784</v>
       </c>
       <c r="I33" t="n">
-        <v>0.0419525943915665</v>
+        <v>0.04140277326332537</v>
       </c>
       <c r="J33" t="n">
-        <v>0.04872880584758205</v>
+        <v>0.04564332626598652</v>
       </c>
       <c r="K33" t="n">
-        <v>0.04147767464603751</v>
+        <v>0.041137089703356</v>
       </c>
       <c r="L33" t="n">
-        <v>0.04105618944429491</v>
+        <v>0.04088435590423223</v>
       </c>
       <c r="M33" t="n">
-        <v>0.05274564318697297</v>
+        <v>0.0481415243180499</v>
       </c>
       <c r="N33" t="n">
-        <v>0.04922124169039242</v>
+        <v>0.04579149546454445</v>
       </c>
       <c r="O33" t="n">
-        <v>0.08819299338468259</v>
+        <v>0.07434210557970765</v>
       </c>
       <c r="P33" t="n">
-        <v>0.06447746714562878</v>
+        <v>0.05529145631136096</v>
       </c>
       <c r="Q33" t="n">
-        <v>0.0479480677798205</v>
+        <v>0.04516199044825083</v>
       </c>
       <c r="R33" t="n">
-        <v>0.04133706051958963</v>
+        <v>0.04103683919982738</v>
       </c>
       <c r="S33" t="n">
-        <v>0.0415055472422791</v>
+        <v>0.04117451092037805</v>
       </c>
       <c r="T33" t="n">
-        <v>0.05267579538489608</v>
+        <v>0.04786690783620032</v>
       </c>
       <c r="U33" t="n">
-        <v>0.222615417411075</v>
+        <v>0.2189601474719332</v>
       </c>
       <c r="V33" t="n">
-        <v>0.04916282987238629</v>
+        <v>0.04596470998903484</v>
       </c>
       <c r="W33" t="n">
-        <v>0.2484612532560781</v>
+        <v>0.2420779602751457</v>
       </c>
       <c r="X33" t="n">
-        <v>0.05210779333818796</v>
+        <v>0.04754241259965716</v>
       </c>
       <c r="Y33" t="n">
-        <v>0.05772817679067717</v>
+        <v>0.05077732656124505</v>
       </c>
       <c r="Z33" t="n">
-        <v>0.1992362308648377</v>
+        <v>0.1974559568805685</v>
       </c>
       <c r="AA33" t="n">
-        <v>0.04273574385728519</v>
+        <v>0.04187708480228634</v>
       </c>
       <c r="AB33" t="n">
-        <v>0.05274094997134137</v>
+        <v>0.04778646199815955</v>
       </c>
     </row>
   </sheetData>
@@ -24118,85 +24118,85 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.04006977246350605</v>
+        <v>0.0399810742150012</v>
       </c>
       <c r="C33" t="n">
-        <v>0.03654877417064818</v>
+        <v>0.0361968667470526</v>
       </c>
       <c r="D33" t="n">
-        <v>0.04092665934872378</v>
+        <v>0.04048631104247378</v>
       </c>
       <c r="E33" t="n">
-        <v>0.01323746688864951</v>
+        <v>0.01298619495878066</v>
       </c>
       <c r="F33" t="n">
-        <v>0.05583542881961148</v>
+        <v>0.04923229225337072</v>
       </c>
       <c r="G33" t="n">
-        <v>0.04300401027563786</v>
+        <v>0.04181490545970264</v>
       </c>
       <c r="H33" t="n">
-        <v>0.04337109825004547</v>
+        <v>0.04188846148194607</v>
       </c>
       <c r="I33" t="n">
-        <v>0.04209917740985565</v>
+        <v>0.04116552656683082</v>
       </c>
       <c r="J33" t="n">
-        <v>0.04558243810367314</v>
+        <v>0.043329793001544</v>
       </c>
       <c r="K33" t="n">
-        <v>0.04270996861610522</v>
+        <v>0.0415723394192041</v>
       </c>
       <c r="L33" t="n">
-        <v>0.04157290407823534</v>
+        <v>0.04092821459561311</v>
       </c>
       <c r="M33" t="n">
-        <v>0.05073181720310835</v>
+        <v>0.04636610417124321</v>
       </c>
       <c r="N33" t="n">
-        <v>0.04456547133401331</v>
+        <v>0.04265743082107576</v>
       </c>
       <c r="O33" t="n">
-        <v>0.07505858774106282</v>
+        <v>0.06463888320202299</v>
       </c>
       <c r="P33" t="n">
-        <v>0.06110632958451456</v>
+        <v>0.05305681553147763</v>
       </c>
       <c r="Q33" t="n">
-        <v>0.04330173574692645</v>
+        <v>0.04193834976007707</v>
       </c>
       <c r="R33" t="n">
-        <v>0.04103138293134815</v>
+        <v>0.04053327136183419</v>
       </c>
       <c r="S33" t="n">
-        <v>0.0476020495202825</v>
+        <v>0.04466236752229944</v>
       </c>
       <c r="T33" t="n">
-        <v>0.0501708727414218</v>
+        <v>0.04595820978978404</v>
       </c>
       <c r="U33" t="n">
-        <v>0.2198598949514063</v>
+        <v>0.2164323605115914</v>
       </c>
       <c r="V33" t="n">
-        <v>0.04413865907004822</v>
+        <v>0.04250448504720802</v>
       </c>
       <c r="W33" t="n">
-        <v>0.235897646187589</v>
+        <v>0.2335437278269191</v>
       </c>
       <c r="X33" t="n">
-        <v>0.05193309629939499</v>
+        <v>0.04717195852462142</v>
       </c>
       <c r="Y33" t="n">
-        <v>0.05165577734682149</v>
+        <v>0.04682067447135357</v>
       </c>
       <c r="Z33" t="n">
-        <v>0.1938747857152003</v>
+        <v>0.1934503549177903</v>
       </c>
       <c r="AA33" t="n">
-        <v>0.04285583250888383</v>
+        <v>0.0416309503362696</v>
       </c>
       <c r="AB33" t="n">
-        <v>0.04940096454035028</v>
+        <v>0.04540139955564544</v>
       </c>
     </row>
   </sheetData>
@@ -27090,85 +27090,85 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.04127500496424901</v>
+        <v>0.04115000404657275</v>
       </c>
       <c r="C33" t="n">
-        <v>0.03834433480772936</v>
+        <v>0.03777213861901794</v>
       </c>
       <c r="D33" t="n">
-        <v>0.04197634875874122</v>
+        <v>0.04155117922322864</v>
       </c>
       <c r="E33" t="n">
-        <v>0.03185640462116668</v>
+        <v>0.02457680351897638</v>
       </c>
       <c r="F33" t="n">
-        <v>0.04482542216912495</v>
+        <v>0.04321843915536953</v>
       </c>
       <c r="G33" t="n">
-        <v>0.04383603298108792</v>
+        <v>0.04273184015656853</v>
       </c>
       <c r="H33" t="n">
-        <v>0.04716755796402449</v>
+        <v>0.0445210160194646</v>
       </c>
       <c r="I33" t="n">
-        <v>0.04375222735890237</v>
+        <v>0.04258429518019675</v>
       </c>
       <c r="J33" t="n">
-        <v>0.0482933819248233</v>
+        <v>0.04541516856259119</v>
       </c>
       <c r="K33" t="n">
-        <v>0.04433820055434536</v>
+        <v>0.04300907398954037</v>
       </c>
       <c r="L33" t="n">
-        <v>0.04138516243575263</v>
+        <v>0.04121315898778875</v>
       </c>
       <c r="M33" t="n">
-        <v>0.04604861413514039</v>
+        <v>0.04400440053944735</v>
       </c>
       <c r="N33" t="n">
-        <v>0.04538873185583776</v>
+        <v>0.04356940853541125</v>
       </c>
       <c r="O33" t="n">
-        <v>0.06787489019854445</v>
+        <v>0.06024589905566328</v>
       </c>
       <c r="P33" t="n">
-        <v>0.05579050951522833</v>
+        <v>0.04998721013294777</v>
       </c>
       <c r="Q33" t="n">
-        <v>0.04620748322460998</v>
+        <v>0.04407667316062575</v>
       </c>
       <c r="R33" t="n">
-        <v>0.04503701548251191</v>
+        <v>0.0433090405363916</v>
       </c>
       <c r="S33" t="n">
-        <v>0.04143214244241721</v>
+        <v>0.04124735692273605</v>
       </c>
       <c r="T33" t="n">
-        <v>0.05066990228476726</v>
+        <v>0.04661713233397114</v>
       </c>
       <c r="U33" t="n">
-        <v>0.2227028059464788</v>
+        <v>0.2192811497616645</v>
       </c>
       <c r="V33" t="n">
-        <v>0.05304697049401671</v>
+        <v>0.04844933397073399</v>
       </c>
       <c r="W33" t="n">
-        <v>0.2586615543864533</v>
+        <v>0.2486189711914966</v>
       </c>
       <c r="X33" t="n">
-        <v>0.0417596953350482</v>
+        <v>0.04142793635947505</v>
       </c>
       <c r="Y33" t="n">
-        <v>0.06097388348699918</v>
+        <v>0.05290159885695409</v>
       </c>
       <c r="Z33" t="n">
-        <v>0.2096800555514892</v>
+        <v>0.2048056536868829</v>
       </c>
       <c r="AA33" t="n">
-        <v>0.04352023564942056</v>
+        <v>0.0424797441342768</v>
       </c>
       <c r="AB33" t="n">
-        <v>0.04359310862590809</v>
+        <v>0.04246676180605989</v>
       </c>
     </row>
   </sheetData>
@@ -30062,85 +30062,85 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.04072980680291559</v>
+        <v>0.04066661226967552</v>
       </c>
       <c r="C33" t="n">
-        <v>0.03752630429288518</v>
+        <v>0.03706773859896629</v>
       </c>
       <c r="D33" t="n">
-        <v>0.04093251769739446</v>
+        <v>0.04078250188586775</v>
       </c>
       <c r="E33" t="n">
-        <v>0.02456107912421427</v>
+        <v>0.02005755425542129</v>
       </c>
       <c r="F33" t="n">
-        <v>0.0524129636857865</v>
+        <v>0.04756086152686201</v>
       </c>
       <c r="G33" t="n">
-        <v>0.0431649974545673</v>
+        <v>0.04219259348471126</v>
       </c>
       <c r="H33" t="n">
-        <v>0.04525709268062417</v>
+        <v>0.04325191955306204</v>
       </c>
       <c r="I33" t="n">
-        <v>0.04158657829467531</v>
+        <v>0.04116157867250363</v>
       </c>
       <c r="J33" t="n">
-        <v>0.04863141267432083</v>
+        <v>0.0454785868143882</v>
       </c>
       <c r="K33" t="n">
-        <v>0.04241615637263969</v>
+        <v>0.04169875648791591</v>
       </c>
       <c r="L33" t="n">
-        <v>0.0409687153449848</v>
+        <v>0.04081036942491347</v>
       </c>
       <c r="M33" t="n">
-        <v>0.06323328617296306</v>
+        <v>0.0542769668274658</v>
       </c>
       <c r="N33" t="n">
-        <v>0.04623305760642238</v>
+        <v>0.043905366868523</v>
       </c>
       <c r="O33" t="n">
-        <v>0.08284323876756493</v>
+        <v>0.07053843926666505</v>
       </c>
       <c r="P33" t="n">
-        <v>0.05841249559733913</v>
+        <v>0.05153956708879528</v>
       </c>
       <c r="Q33" t="n">
-        <v>0.04915514652322554</v>
+        <v>0.04581587330976418</v>
       </c>
       <c r="R33" t="n">
-        <v>0.04206916503044394</v>
+        <v>0.04143641979250596</v>
       </c>
       <c r="S33" t="n">
-        <v>0.04125617238738912</v>
+        <v>0.0409937266879089</v>
       </c>
       <c r="T33" t="n">
-        <v>0.05207640672512738</v>
+        <v>0.04730977529427168</v>
       </c>
       <c r="U33" t="n">
-        <v>0.2247797396464061</v>
+        <v>0.220138084926861</v>
       </c>
       <c r="V33" t="n">
-        <v>0.04863876513188191</v>
+        <v>0.04559876634622436</v>
       </c>
       <c r="W33" t="n">
-        <v>0.2499245986056365</v>
+        <v>0.2427470700185271</v>
       </c>
       <c r="X33" t="n">
-        <v>0.0466502587465978</v>
+        <v>0.04418293111889163</v>
       </c>
       <c r="Y33" t="n">
-        <v>0.05583600005350259</v>
+        <v>0.04967030606105012</v>
       </c>
       <c r="Z33" t="n">
-        <v>0.2010485348616716</v>
+        <v>0.1987321816732843</v>
       </c>
       <c r="AA33" t="n">
-        <v>0.04270904066392272</v>
+        <v>0.04183964544743874</v>
       </c>
       <c r="AB33" t="n">
-        <v>0.04718211297527209</v>
+        <v>0.04439248447413194</v>
       </c>
     </row>
   </sheetData>
